--- a/北部山头3940平台2026/7、单日数据/北部山头3940平台-0922/二次圈矿成果_auto/3940平台 0922炮孔数据报告.xlsx
+++ b/北部山头3940平台2026/7、单日数据/北部山头3940平台-0922/二次圈矿成果_auto/3940平台 0922炮孔数据报告.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -514,23 +514,23 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>0.500-1.000</t>
+          <t>1.500-3.000</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>4907.426</v>
+        <v>948.674</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>13250.049</v>
+        <v>2561.42</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.99</v>
+        <v>1.727</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>131.175</v>
+        <v>44.227</v>
       </c>
     </row>
     <row r="4">
@@ -541,107 +541,213 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="7" t="n">
-        <v>4907.426</v>
+        <v>948.674</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>13250.049</v>
+        <v>2561.42</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>0.99</v>
+        <v>1.727</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>131.175</v>
+        <v>44.227</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="9" t="n">
-        <v>4907.426</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>13250.049</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>131.175</v>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>1.000-1.500</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1090.677</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>2944.827</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>39.25</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>小计</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="7" t="n">
+        <v>1090.677</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>2944.827</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>39.25</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>炮孔品位统计（孔数）</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>0.500-1.000</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>2728.153</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>7366.014</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>60.675</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>0.500-1.000</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>561.562</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1516.216</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>10.538</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>小计</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="7" t="n">
+        <v>3289.715</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>8882.23</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>71.21299999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="9" t="n">
+        <v>5329.066</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>14388.478</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>154.691</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>炮孔品位统计（孔数）</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>≥3</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>1.5-3</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D13" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>1-1.5</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F13" s="5" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>0.5-1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B14" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>&lt;0.5</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>合计孔数</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F14" s="5" t="n">
         <v>23</v>
       </c>
     </row>
